--- a/app/static/storage/DI January to June 2026.xlsx
+++ b/app/static/storage/DI January to June 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PyZar\app\static\storage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38908EB4-A66D-422D-AF85-98CB27AE895D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19E06C9C-6FDA-4B2E-A3A2-B9DB07181F72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="First page" sheetId="1" r:id="rId1"/>
@@ -1582,30 +1582,43 @@
     <xf numFmtId="1" fontId="13" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="15" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1619,10 +1632,6 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="49" fontId="15" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -1638,15 +1647,6 @@
     <xf numFmtId="49" fontId="15" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1972,86 +1972,86 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="69" t="s">
+      <c r="A1" s="75" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="70"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="70"/>
-      <c r="E1" s="70"/>
-      <c r="F1" s="70"/>
-      <c r="G1" s="70"/>
-      <c r="H1" s="70"/>
-      <c r="I1" s="70"/>
-      <c r="J1" s="70"/>
-      <c r="K1" s="70"/>
-      <c r="L1" s="70"/>
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
+      <c r="H1" s="76"/>
+      <c r="I1" s="76"/>
+      <c r="J1" s="76"/>
+      <c r="K1" s="76"/>
+      <c r="L1" s="76"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="76" t="s">
+      <c r="A2" s="78" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="70"/>
-      <c r="C2" s="70"/>
-      <c r="D2" s="70"/>
-      <c r="E2" s="70"/>
-      <c r="F2" s="70"/>
-      <c r="G2" s="70"/>
-      <c r="H2" s="70"/>
-      <c r="I2" s="70"/>
-      <c r="J2" s="70"/>
-      <c r="K2" s="70"/>
-      <c r="L2" s="70"/>
+      <c r="B2" s="76"/>
+      <c r="C2" s="76"/>
+      <c r="D2" s="76"/>
+      <c r="E2" s="76"/>
+      <c r="F2" s="76"/>
+      <c r="G2" s="76"/>
+      <c r="H2" s="76"/>
+      <c r="I2" s="76"/>
+      <c r="J2" s="76"/>
+      <c r="K2" s="76"/>
+      <c r="L2" s="76"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="72" t="s">
+      <c r="C4" s="77" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="70"/>
-      <c r="E4" s="70"/>
-      <c r="F4" s="70"/>
-      <c r="G4" s="70"/>
-      <c r="H4" s="70"/>
-      <c r="I4" s="70"/>
-      <c r="J4" s="70"/>
-      <c r="K4" s="70"/>
-      <c r="L4" s="70"/>
+      <c r="D4" s="76"/>
+      <c r="E4" s="76"/>
+      <c r="F4" s="76"/>
+      <c r="G4" s="76"/>
+      <c r="H4" s="76"/>
+      <c r="I4" s="76"/>
+      <c r="J4" s="76"/>
+      <c r="K4" s="76"/>
+      <c r="L4" s="76"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="72" t="s">
-        <v>5</v>
-      </c>
-      <c r="D5" s="70"/>
-      <c r="E5" s="70"/>
-      <c r="F5" s="70"/>
-      <c r="G5" s="70"/>
-      <c r="H5" s="70"/>
-      <c r="I5" s="70"/>
-      <c r="J5" s="70"/>
-      <c r="K5" s="70"/>
-      <c r="L5" s="70"/>
+      <c r="C5" s="77" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" s="76"/>
+      <c r="E5" s="76"/>
+      <c r="F5" s="76"/>
+      <c r="G5" s="76"/>
+      <c r="H5" s="76"/>
+      <c r="I5" s="76"/>
+      <c r="J5" s="76"/>
+      <c r="K5" s="76"/>
+      <c r="L5" s="76"/>
     </row>
     <row r="7" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="73" t="s">
+      <c r="A7" s="68" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="68"/>
-      <c r="C7" s="68"/>
-      <c r="D7" s="68"/>
-      <c r="E7" s="68"/>
-      <c r="F7" s="68"/>
-      <c r="G7" s="68"/>
-      <c r="H7" s="68"/>
-      <c r="I7" s="68"/>
-      <c r="J7" s="68"/>
-      <c r="K7" s="68"/>
-      <c r="L7" s="68"/>
+      <c r="B7" s="69"/>
+      <c r="C7" s="69"/>
+      <c r="D7" s="69"/>
+      <c r="E7" s="69"/>
+      <c r="F7" s="69"/>
+      <c r="G7" s="69"/>
+      <c r="H7" s="69"/>
+      <c r="I7" s="69"/>
+      <c r="J7" s="69"/>
+      <c r="K7" s="69"/>
+      <c r="L7" s="69"/>
     </row>
     <row r="8" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
@@ -2092,20 +2092,20 @@
       </c>
     </row>
     <row r="9" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="73" t="s">
+      <c r="A9" s="68" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="68"/>
-      <c r="C9" s="68"/>
-      <c r="D9" s="68"/>
-      <c r="E9" s="68"/>
-      <c r="F9" s="68"/>
-      <c r="G9" s="68"/>
-      <c r="H9" s="68"/>
-      <c r="I9" s="68"/>
-      <c r="J9" s="68"/>
-      <c r="K9" s="68"/>
-      <c r="L9" s="68"/>
+      <c r="B9" s="69"/>
+      <c r="C9" s="69"/>
+      <c r="D9" s="69"/>
+      <c r="E9" s="69"/>
+      <c r="F9" s="69"/>
+      <c r="G9" s="69"/>
+      <c r="H9" s="69"/>
+      <c r="I9" s="69"/>
+      <c r="J9" s="69"/>
+      <c r="K9" s="69"/>
+      <c r="L9" s="69"/>
     </row>
     <row r="10" spans="1:12" ht="51" x14ac:dyDescent="0.25">
       <c r="A10" s="11">
@@ -2243,7 +2243,7 @@
       <c r="I13" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="J13" s="88" t="s">
+      <c r="J13" s="67" t="s">
         <v>339</v>
       </c>
       <c r="K13" s="11"/>
@@ -2829,35 +2829,35 @@
       <c r="A30" s="4">
         <v>20</v>
       </c>
-      <c r="B30" s="67" t="s">
+      <c r="B30" s="72" t="s">
         <v>81</v>
       </c>
-      <c r="C30" s="68"/>
-      <c r="D30" s="68"/>
-      <c r="E30" s="68"/>
-      <c r="F30" s="68"/>
-      <c r="G30" s="68"/>
-      <c r="H30" s="68"/>
-      <c r="I30" s="68"/>
-      <c r="J30" s="68"/>
-      <c r="K30" s="68"/>
-      <c r="L30" s="68"/>
+      <c r="C30" s="69"/>
+      <c r="D30" s="69"/>
+      <c r="E30" s="69"/>
+      <c r="F30" s="69"/>
+      <c r="G30" s="69"/>
+      <c r="H30" s="69"/>
+      <c r="I30" s="69"/>
+      <c r="J30" s="69"/>
+      <c r="K30" s="69"/>
+      <c r="L30" s="69"/>
     </row>
     <row r="32" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A32" s="73" t="s">
+      <c r="A32" s="68" t="s">
         <v>82</v>
       </c>
-      <c r="B32" s="74"/>
-      <c r="C32" s="74"/>
-      <c r="D32" s="74"/>
-      <c r="E32" s="74"/>
-      <c r="F32" s="74"/>
-      <c r="G32" s="74"/>
-      <c r="H32" s="74"/>
-      <c r="I32" s="74"/>
-      <c r="J32" s="74"/>
-      <c r="K32" s="74"/>
-      <c r="L32" s="74"/>
+      <c r="B32" s="71"/>
+      <c r="C32" s="71"/>
+      <c r="D32" s="71"/>
+      <c r="E32" s="71"/>
+      <c r="F32" s="71"/>
+      <c r="G32" s="71"/>
+      <c r="H32" s="71"/>
+      <c r="I32" s="71"/>
+      <c r="J32" s="71"/>
+      <c r="K32" s="71"/>
+      <c r="L32" s="71"/>
     </row>
     <row r="33" spans="1:12" ht="229.5" x14ac:dyDescent="0.25">
       <c r="A33" s="24">
@@ -3127,35 +3127,35 @@
       <c r="A42" s="4">
         <v>9</v>
       </c>
-      <c r="B42" s="77" t="s">
+      <c r="B42" s="73" t="s">
         <v>110</v>
       </c>
-      <c r="C42" s="75"/>
-      <c r="D42" s="75"/>
-      <c r="E42" s="75"/>
-      <c r="F42" s="75"/>
-      <c r="G42" s="75"/>
-      <c r="H42" s="75"/>
-      <c r="I42" s="75"/>
-      <c r="J42" s="75"/>
-      <c r="K42" s="75"/>
-      <c r="L42" s="75"/>
+      <c r="C42" s="74"/>
+      <c r="D42" s="74"/>
+      <c r="E42" s="74"/>
+      <c r="F42" s="74"/>
+      <c r="G42" s="74"/>
+      <c r="H42" s="74"/>
+      <c r="I42" s="74"/>
+      <c r="J42" s="74"/>
+      <c r="K42" s="74"/>
+      <c r="L42" s="74"/>
     </row>
     <row r="44" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A44" s="73" t="s">
+      <c r="A44" s="68" t="s">
         <v>111</v>
       </c>
-      <c r="B44" s="68"/>
-      <c r="C44" s="68"/>
-      <c r="D44" s="68"/>
-      <c r="E44" s="68"/>
-      <c r="F44" s="68"/>
-      <c r="G44" s="68"/>
-      <c r="H44" s="68"/>
-      <c r="I44" s="74"/>
-      <c r="J44" s="68"/>
-      <c r="K44" s="68"/>
-      <c r="L44" s="68"/>
+      <c r="B44" s="69"/>
+      <c r="C44" s="69"/>
+      <c r="D44" s="69"/>
+      <c r="E44" s="69"/>
+      <c r="F44" s="69"/>
+      <c r="G44" s="69"/>
+      <c r="H44" s="69"/>
+      <c r="I44" s="71"/>
+      <c r="J44" s="69"/>
+      <c r="K44" s="69"/>
+      <c r="L44" s="69"/>
     </row>
     <row r="45" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A45" s="11">
@@ -3281,130 +3281,130 @@
       <c r="A49" s="4">
         <v>4</v>
       </c>
-      <c r="B49" s="67" t="s">
+      <c r="B49" s="72" t="s">
         <v>121</v>
       </c>
-      <c r="C49" s="68"/>
-      <c r="D49" s="68"/>
-      <c r="E49" s="68"/>
-      <c r="F49" s="68"/>
-      <c r="G49" s="68"/>
-      <c r="H49" s="68"/>
-      <c r="I49" s="75"/>
-      <c r="J49" s="68"/>
-      <c r="K49" s="68"/>
-      <c r="L49" s="68"/>
+      <c r="C49" s="69"/>
+      <c r="D49" s="69"/>
+      <c r="E49" s="69"/>
+      <c r="F49" s="69"/>
+      <c r="G49" s="69"/>
+      <c r="H49" s="69"/>
+      <c r="I49" s="74"/>
+      <c r="J49" s="69"/>
+      <c r="K49" s="69"/>
+      <c r="L49" s="69"/>
     </row>
     <row r="51" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A51" s="73" t="s">
+      <c r="A51" s="68" t="s">
         <v>122</v>
       </c>
-      <c r="B51" s="68"/>
-      <c r="C51" s="68"/>
-      <c r="D51" s="68"/>
-      <c r="E51" s="68"/>
-      <c r="F51" s="68"/>
-      <c r="G51" s="68"/>
-      <c r="H51" s="68"/>
-      <c r="I51" s="68"/>
-      <c r="J51" s="68"/>
-      <c r="K51" s="68"/>
-      <c r="L51" s="68"/>
+      <c r="B51" s="69"/>
+      <c r="C51" s="69"/>
+      <c r="D51" s="69"/>
+      <c r="E51" s="69"/>
+      <c r="F51" s="69"/>
+      <c r="G51" s="69"/>
+      <c r="H51" s="69"/>
+      <c r="I51" s="69"/>
+      <c r="J51" s="69"/>
+      <c r="K51" s="69"/>
+      <c r="L51" s="69"/>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52" s="4">
         <v>0</v>
       </c>
-      <c r="B52" s="67" t="s">
+      <c r="B52" s="72" t="s">
         <v>123</v>
       </c>
-      <c r="C52" s="68"/>
-      <c r="D52" s="68"/>
-      <c r="E52" s="68"/>
-      <c r="F52" s="68"/>
-      <c r="G52" s="68"/>
-      <c r="H52" s="68"/>
-      <c r="I52" s="68"/>
-      <c r="J52" s="68"/>
-      <c r="K52" s="68"/>
-      <c r="L52" s="68"/>
+      <c r="C52" s="69"/>
+      <c r="D52" s="69"/>
+      <c r="E52" s="69"/>
+      <c r="F52" s="69"/>
+      <c r="G52" s="69"/>
+      <c r="H52" s="69"/>
+      <c r="I52" s="69"/>
+      <c r="J52" s="69"/>
+      <c r="K52" s="69"/>
+      <c r="L52" s="69"/>
     </row>
     <row r="54" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A54" s="73" t="s">
+      <c r="A54" s="68" t="s">
         <v>124</v>
       </c>
-      <c r="B54" s="68"/>
-      <c r="C54" s="68"/>
-      <c r="D54" s="68"/>
-      <c r="E54" s="68"/>
-      <c r="F54" s="68"/>
-      <c r="G54" s="68"/>
-      <c r="H54" s="68"/>
-      <c r="I54" s="68"/>
-      <c r="J54" s="68"/>
-      <c r="K54" s="68"/>
-      <c r="L54" s="68"/>
+      <c r="B54" s="69"/>
+      <c r="C54" s="69"/>
+      <c r="D54" s="69"/>
+      <c r="E54" s="69"/>
+      <c r="F54" s="69"/>
+      <c r="G54" s="69"/>
+      <c r="H54" s="69"/>
+      <c r="I54" s="69"/>
+      <c r="J54" s="69"/>
+      <c r="K54" s="69"/>
+      <c r="L54" s="69"/>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A55" s="4">
         <v>0</v>
       </c>
-      <c r="B55" s="67" t="s">
+      <c r="B55" s="72" t="s">
         <v>125</v>
       </c>
-      <c r="C55" s="68"/>
-      <c r="D55" s="68"/>
-      <c r="E55" s="68"/>
-      <c r="F55" s="68"/>
-      <c r="G55" s="68"/>
-      <c r="H55" s="68"/>
-      <c r="I55" s="68"/>
-      <c r="J55" s="68"/>
-      <c r="K55" s="68"/>
-      <c r="L55" s="68"/>
+      <c r="C55" s="69"/>
+      <c r="D55" s="69"/>
+      <c r="E55" s="69"/>
+      <c r="F55" s="69"/>
+      <c r="G55" s="69"/>
+      <c r="H55" s="69"/>
+      <c r="I55" s="69"/>
+      <c r="J55" s="69"/>
+      <c r="K55" s="69"/>
+      <c r="L55" s="69"/>
     </row>
     <row r="57" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A57" s="73" t="s">
+      <c r="A57" s="68" t="s">
         <v>126</v>
       </c>
-      <c r="B57" s="68"/>
-      <c r="C57" s="68"/>
-      <c r="D57" s="68"/>
-      <c r="E57" s="68"/>
-      <c r="F57" s="68"/>
-      <c r="G57" s="68"/>
-      <c r="H57" s="68"/>
-      <c r="I57" s="68"/>
-      <c r="J57" s="68"/>
-      <c r="K57" s="68"/>
-      <c r="L57" s="68"/>
+      <c r="B57" s="69"/>
+      <c r="C57" s="69"/>
+      <c r="D57" s="69"/>
+      <c r="E57" s="69"/>
+      <c r="F57" s="69"/>
+      <c r="G57" s="69"/>
+      <c r="H57" s="69"/>
+      <c r="I57" s="69"/>
+      <c r="J57" s="69"/>
+      <c r="K57" s="69"/>
+      <c r="L57" s="69"/>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A58" s="4">
         <v>0</v>
       </c>
-      <c r="B58" s="67" t="s">
+      <c r="B58" s="72" t="s">
         <v>127</v>
       </c>
-      <c r="C58" s="68"/>
-      <c r="D58" s="68"/>
-      <c r="E58" s="68"/>
-      <c r="F58" s="68"/>
-      <c r="G58" s="68"/>
-      <c r="H58" s="68"/>
-      <c r="I58" s="68"/>
-      <c r="J58" s="68"/>
-      <c r="K58" s="68"/>
-      <c r="L58" s="68"/>
+      <c r="C58" s="69"/>
+      <c r="D58" s="69"/>
+      <c r="E58" s="69"/>
+      <c r="F58" s="69"/>
+      <c r="G58" s="69"/>
+      <c r="H58" s="69"/>
+      <c r="I58" s="69"/>
+      <c r="J58" s="69"/>
+      <c r="K58" s="69"/>
+      <c r="L58" s="69"/>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A60" s="5">
         <v>13</v>
       </c>
-      <c r="B60" s="67" t="s">
+      <c r="B60" s="72" t="s">
         <v>110</v>
       </c>
-      <c r="C60" s="68"/>
+      <c r="C60" s="69"/>
       <c r="D60" s="2"/>
       <c r="E60" s="2"/>
       <c r="F60" s="2"/>
@@ -3419,10 +3419,10 @@
       <c r="A61" s="5">
         <v>33</v>
       </c>
-      <c r="B61" s="67" t="s">
+      <c r="B61" s="72" t="s">
         <v>128</v>
       </c>
-      <c r="C61" s="68"/>
+      <c r="C61" s="69"/>
       <c r="D61" s="2"/>
       <c r="E61" s="2"/>
       <c r="F61" s="2"/>
@@ -3434,36 +3434,36 @@
       <c r="L61" s="12"/>
     </row>
     <row r="63" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A63" s="73" t="s">
+      <c r="A63" s="68" t="s">
         <v>129</v>
       </c>
-      <c r="B63" s="68"/>
-      <c r="C63" s="68"/>
-      <c r="D63" s="68"/>
-      <c r="E63" s="68"/>
-      <c r="F63" s="68"/>
-      <c r="G63" s="68"/>
-      <c r="H63" s="68"/>
-      <c r="I63" s="68"/>
-      <c r="J63" s="68"/>
-      <c r="K63" s="68"/>
-      <c r="L63" s="68"/>
+      <c r="B63" s="69"/>
+      <c r="C63" s="69"/>
+      <c r="D63" s="69"/>
+      <c r="E63" s="69"/>
+      <c r="F63" s="69"/>
+      <c r="G63" s="69"/>
+      <c r="H63" s="69"/>
+      <c r="I63" s="69"/>
+      <c r="J63" s="69"/>
+      <c r="K63" s="69"/>
+      <c r="L63" s="69"/>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A64" s="71" t="s">
+      <c r="A64" s="70" t="s">
         <v>130</v>
       </c>
-      <c r="B64" s="68"/>
-      <c r="C64" s="68"/>
-      <c r="D64" s="68"/>
-      <c r="E64" s="68"/>
-      <c r="F64" s="68"/>
-      <c r="G64" s="68"/>
-      <c r="H64" s="68"/>
-      <c r="I64" s="68"/>
-      <c r="J64" s="68"/>
-      <c r="K64" s="68"/>
-      <c r="L64" s="68"/>
+      <c r="B64" s="69"/>
+      <c r="C64" s="69"/>
+      <c r="D64" s="69"/>
+      <c r="E64" s="69"/>
+      <c r="F64" s="69"/>
+      <c r="G64" s="69"/>
+      <c r="H64" s="69"/>
+      <c r="I64" s="69"/>
+      <c r="J64" s="69"/>
+      <c r="K64" s="69"/>
+      <c r="L64" s="69"/>
     </row>
     <row r="65" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A65" s="11">
@@ -4330,20 +4330,20 @@
       </c>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A90" s="71" t="s">
+      <c r="A90" s="70" t="s">
         <v>238</v>
       </c>
-      <c r="B90" s="68"/>
-      <c r="C90" s="68"/>
-      <c r="D90" s="68"/>
-      <c r="E90" s="68"/>
-      <c r="F90" s="68"/>
-      <c r="G90" s="68"/>
-      <c r="H90" s="68"/>
-      <c r="I90" s="74"/>
-      <c r="J90" s="74"/>
-      <c r="K90" s="74"/>
-      <c r="L90" s="74"/>
+      <c r="B90" s="69"/>
+      <c r="C90" s="69"/>
+      <c r="D90" s="69"/>
+      <c r="E90" s="69"/>
+      <c r="F90" s="69"/>
+      <c r="G90" s="69"/>
+      <c r="H90" s="69"/>
+      <c r="I90" s="71"/>
+      <c r="J90" s="71"/>
+      <c r="K90" s="71"/>
+      <c r="L90" s="71"/>
     </row>
     <row r="91" spans="1:12" ht="204" x14ac:dyDescent="0.25">
       <c r="A91" s="11">
@@ -4732,20 +4732,20 @@
       </c>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A105" s="71" t="s">
+      <c r="A105" s="70" t="s">
         <v>264</v>
       </c>
-      <c r="B105" s="68"/>
-      <c r="C105" s="68"/>
-      <c r="D105" s="68"/>
-      <c r="E105" s="68"/>
-      <c r="F105" s="68"/>
-      <c r="G105" s="68"/>
-      <c r="H105" s="68"/>
-      <c r="I105" s="68"/>
-      <c r="J105" s="68"/>
-      <c r="K105" s="68"/>
-      <c r="L105" s="68"/>
+      <c r="B105" s="69"/>
+      <c r="C105" s="69"/>
+      <c r="D105" s="69"/>
+      <c r="E105" s="69"/>
+      <c r="F105" s="69"/>
+      <c r="G105" s="69"/>
+      <c r="H105" s="69"/>
+      <c r="I105" s="69"/>
+      <c r="J105" s="69"/>
+      <c r="K105" s="69"/>
+      <c r="L105" s="69"/>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A106" s="6"/>
@@ -4762,20 +4762,20 @@
       <c r="L106" s="12"/>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A108" s="71" t="s">
+      <c r="A108" s="70" t="s">
         <v>265</v>
       </c>
-      <c r="B108" s="68"/>
-      <c r="C108" s="68"/>
-      <c r="D108" s="68"/>
-      <c r="E108" s="68"/>
-      <c r="F108" s="68"/>
-      <c r="G108" s="68"/>
-      <c r="H108" s="68"/>
-      <c r="I108" s="68"/>
-      <c r="J108" s="68"/>
-      <c r="K108" s="68"/>
-      <c r="L108" s="68"/>
+      <c r="B108" s="69"/>
+      <c r="C108" s="69"/>
+      <c r="D108" s="69"/>
+      <c r="E108" s="69"/>
+      <c r="F108" s="69"/>
+      <c r="G108" s="69"/>
+      <c r="H108" s="69"/>
+      <c r="I108" s="69"/>
+      <c r="J108" s="69"/>
+      <c r="K108" s="69"/>
+      <c r="L108" s="69"/>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A109" s="6"/>
@@ -4792,20 +4792,20 @@
       <c r="L109" s="12"/>
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A111" s="71" t="s">
+      <c r="A111" s="70" t="s">
         <v>266</v>
       </c>
-      <c r="B111" s="68"/>
-      <c r="C111" s="68"/>
-      <c r="D111" s="68"/>
-      <c r="E111" s="68"/>
-      <c r="F111" s="68"/>
-      <c r="G111" s="68"/>
-      <c r="H111" s="68"/>
-      <c r="I111" s="68"/>
-      <c r="J111" s="68"/>
-      <c r="K111" s="68"/>
-      <c r="L111" s="68"/>
+      <c r="B111" s="69"/>
+      <c r="C111" s="69"/>
+      <c r="D111" s="69"/>
+      <c r="E111" s="69"/>
+      <c r="F111" s="69"/>
+      <c r="G111" s="69"/>
+      <c r="H111" s="69"/>
+      <c r="I111" s="69"/>
+      <c r="J111" s="69"/>
+      <c r="K111" s="69"/>
+      <c r="L111" s="69"/>
     </row>
     <row r="112" spans="1:12" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A112" s="8"/>
@@ -4825,10 +4825,10 @@
       <c r="A114" s="5">
         <v>37</v>
       </c>
-      <c r="B114" s="67" t="s">
+      <c r="B114" s="72" t="s">
         <v>267</v>
       </c>
-      <c r="C114" s="68"/>
+      <c r="C114" s="69"/>
       <c r="D114" s="2"/>
       <c r="E114" s="2"/>
       <c r="F114" s="2"/>
@@ -4841,16 +4841,6 @@
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="A7:L7"/>
-    <mergeCell ref="A105:L105"/>
-    <mergeCell ref="A57:L57"/>
-    <mergeCell ref="A90:L90"/>
-    <mergeCell ref="A108:L108"/>
-    <mergeCell ref="A32:L32"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B42:L42"/>
-    <mergeCell ref="A54:L54"/>
     <mergeCell ref="B114:C114"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="B55:L55"/>
@@ -4867,6 +4857,16 @@
     <mergeCell ref="A2:L2"/>
     <mergeCell ref="B58:L58"/>
     <mergeCell ref="B52:L52"/>
+    <mergeCell ref="A7:L7"/>
+    <mergeCell ref="A105:L105"/>
+    <mergeCell ref="A57:L57"/>
+    <mergeCell ref="A90:L90"/>
+    <mergeCell ref="A108:L108"/>
+    <mergeCell ref="A32:L32"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B42:L42"/>
+    <mergeCell ref="A54:L54"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="133" scale="70" fitToHeight="0" orientation="landscape" r:id="rId1"/>
@@ -4895,75 +4895,75 @@
       <c r="A2" s="65" t="s">
         <v>323</v>
       </c>
-      <c r="B2" s="86" t="s">
+      <c r="B2" s="80" t="s">
         <v>324</v>
       </c>
-      <c r="C2" s="86"/>
-      <c r="D2" s="86"/>
-      <c r="E2" s="86"/>
-      <c r="F2" s="86"/>
-      <c r="G2" s="86"/>
-      <c r="H2" s="86"/>
-      <c r="I2" s="86"/>
-      <c r="J2" s="86"/>
-      <c r="K2" s="86"/>
-      <c r="L2" s="86"/>
-      <c r="M2" s="86"/>
+      <c r="C2" s="80"/>
+      <c r="D2" s="80"/>
+      <c r="E2" s="80"/>
+      <c r="F2" s="80"/>
+      <c r="G2" s="80"/>
+      <c r="H2" s="80"/>
+      <c r="I2" s="80"/>
+      <c r="J2" s="80"/>
+      <c r="K2" s="80"/>
+      <c r="L2" s="80"/>
+      <c r="M2" s="80"/>
     </row>
     <row r="3" spans="1:13" s="48" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="66" t="s">
         <v>325</v>
       </c>
-      <c r="B3" s="86" t="s">
+      <c r="B3" s="80" t="s">
         <v>326</v>
       </c>
-      <c r="C3" s="86"/>
-      <c r="D3" s="86"/>
-      <c r="E3" s="86"/>
-      <c r="F3" s="86"/>
-      <c r="G3" s="86"/>
-      <c r="H3" s="86"/>
-      <c r="I3" s="86"/>
-      <c r="J3" s="86"/>
-      <c r="K3" s="86"/>
-      <c r="L3" s="86"/>
-      <c r="M3" s="86"/>
+      <c r="C3" s="80"/>
+      <c r="D3" s="80"/>
+      <c r="E3" s="80"/>
+      <c r="F3" s="80"/>
+      <c r="G3" s="80"/>
+      <c r="H3" s="80"/>
+      <c r="I3" s="80"/>
+      <c r="J3" s="80"/>
+      <c r="K3" s="80"/>
+      <c r="L3" s="80"/>
+      <c r="M3" s="80"/>
     </row>
     <row r="4" spans="1:13" s="48" customFormat="1" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A4" s="65" t="s">
         <v>327</v>
       </c>
-      <c r="B4" s="86" t="s">
+      <c r="B4" s="80" t="s">
         <v>328</v>
       </c>
-      <c r="C4" s="86"/>
-      <c r="D4" s="86"/>
-      <c r="E4" s="86"/>
-      <c r="F4" s="86"/>
-      <c r="G4" s="86"/>
-      <c r="H4" s="86"/>
-      <c r="I4" s="86"/>
-      <c r="J4" s="86"/>
-      <c r="K4" s="86"/>
-      <c r="L4" s="86"/>
-      <c r="M4" s="86"/>
+      <c r="C4" s="80"/>
+      <c r="D4" s="80"/>
+      <c r="E4" s="80"/>
+      <c r="F4" s="80"/>
+      <c r="G4" s="80"/>
+      <c r="H4" s="80"/>
+      <c r="I4" s="80"/>
+      <c r="J4" s="80"/>
+      <c r="K4" s="80"/>
+      <c r="L4" s="80"/>
+      <c r="M4" s="80"/>
     </row>
     <row r="5" spans="1:13" s="48" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="64"/>
-      <c r="B5" s="87" t="s">
+      <c r="B5" s="81" t="s">
         <v>329</v>
       </c>
-      <c r="C5" s="87"/>
-      <c r="D5" s="87"/>
-      <c r="E5" s="87"/>
-      <c r="F5" s="87"/>
-      <c r="G5" s="87"/>
-      <c r="H5" s="87"/>
-      <c r="I5" s="87"/>
-      <c r="J5" s="87"/>
-      <c r="K5" s="87"/>
-      <c r="L5" s="87"/>
-      <c r="M5" s="87"/>
+      <c r="C5" s="81"/>
+      <c r="D5" s="81"/>
+      <c r="E5" s="81"/>
+      <c r="F5" s="81"/>
+      <c r="G5" s="81"/>
+      <c r="H5" s="81"/>
+      <c r="I5" s="81"/>
+      <c r="J5" s="81"/>
+      <c r="K5" s="81"/>
+      <c r="L5" s="81"/>
+      <c r="M5" s="81"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" s="63"/>
@@ -5029,54 +5029,54 @@
     </row>
     <row r="10" spans="1:13" s="46" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="47"/>
-      <c r="B10" s="81" t="s">
+      <c r="B10" s="79" t="s">
         <v>331</v>
       </c>
-      <c r="C10" s="81"/>
-      <c r="D10" s="81"/>
-      <c r="E10" s="81"/>
-      <c r="F10" s="81"/>
-      <c r="G10" s="81"/>
-      <c r="H10" s="81"/>
-      <c r="I10" s="81"/>
-      <c r="J10" s="81"/>
-      <c r="K10" s="81"/>
-      <c r="L10" s="81"/>
-      <c r="M10" s="81"/>
+      <c r="C10" s="79"/>
+      <c r="D10" s="79"/>
+      <c r="E10" s="79"/>
+      <c r="F10" s="79"/>
+      <c r="G10" s="79"/>
+      <c r="H10" s="79"/>
+      <c r="I10" s="79"/>
+      <c r="J10" s="79"/>
+      <c r="K10" s="79"/>
+      <c r="L10" s="79"/>
+      <c r="M10" s="79"/>
     </row>
     <row r="11" spans="1:13" s="46" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="81" t="s">
+      <c r="A11" s="79" t="s">
         <v>341</v>
       </c>
-      <c r="B11" s="81"/>
-      <c r="C11" s="81"/>
-      <c r="D11" s="81"/>
-      <c r="E11" s="81"/>
-      <c r="F11" s="81"/>
-      <c r="G11" s="81"/>
-      <c r="H11" s="81"/>
-      <c r="I11" s="81"/>
-      <c r="J11" s="81"/>
-      <c r="K11" s="81"/>
-      <c r="L11" s="81"/>
-      <c r="M11" s="81"/>
+      <c r="B11" s="79"/>
+      <c r="C11" s="79"/>
+      <c r="D11" s="79"/>
+      <c r="E11" s="79"/>
+      <c r="F11" s="79"/>
+      <c r="G11" s="79"/>
+      <c r="H11" s="79"/>
+      <c r="I11" s="79"/>
+      <c r="J11" s="79"/>
+      <c r="K11" s="79"/>
+      <c r="L11" s="79"/>
+      <c r="M11" s="79"/>
     </row>
     <row r="12" spans="1:13" s="41" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="81" t="s">
+      <c r="A12" s="79" t="s">
         <v>332</v>
       </c>
-      <c r="B12" s="81"/>
-      <c r="C12" s="81"/>
-      <c r="D12" s="81"/>
-      <c r="E12" s="81"/>
-      <c r="F12" s="81"/>
-      <c r="G12" s="81"/>
-      <c r="H12" s="81"/>
-      <c r="I12" s="81"/>
-      <c r="J12" s="81"/>
-      <c r="K12" s="81"/>
-      <c r="L12" s="81"/>
-      <c r="M12" s="81"/>
+      <c r="B12" s="79"/>
+      <c r="C12" s="79"/>
+      <c r="D12" s="79"/>
+      <c r="E12" s="79"/>
+      <c r="F12" s="79"/>
+      <c r="G12" s="79"/>
+      <c r="H12" s="79"/>
+      <c r="I12" s="79"/>
+      <c r="J12" s="79"/>
+      <c r="K12" s="79"/>
+      <c r="L12" s="79"/>
+      <c r="M12" s="79"/>
     </row>
     <row r="13" spans="1:13" s="41" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A13" s="43"/>
@@ -5156,38 +5156,38 @@
     <row r="18" spans="1:13" s="41" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" s="43"/>
       <c r="B18" s="38"/>
-      <c r="C18" s="82" t="s">
-        <v>5</v>
-      </c>
-      <c r="D18" s="82"/>
+      <c r="C18" s="85" t="s">
+        <v>5</v>
+      </c>
+      <c r="D18" s="85"/>
       <c r="E18" s="42"/>
       <c r="F18" s="42"/>
       <c r="G18" s="42"/>
       <c r="H18" s="42"/>
-      <c r="I18" s="82" t="s">
+      <c r="I18" s="85" t="s">
         <v>337</v>
       </c>
-      <c r="J18" s="82"/>
-      <c r="K18" s="82"/>
+      <c r="J18" s="85"/>
+      <c r="K18" s="85"/>
       <c r="L18" s="42"/>
       <c r="M18" s="36"/>
     </row>
     <row r="19" spans="1:13" s="45" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="35"/>
       <c r="B19" s="38"/>
-      <c r="C19" s="83" t="s">
+      <c r="C19" s="86" t="s">
         <v>333</v>
       </c>
-      <c r="D19" s="83"/>
+      <c r="D19" s="86"/>
       <c r="E19" s="32"/>
       <c r="F19" s="32"/>
       <c r="G19" s="32"/>
       <c r="H19" s="32"/>
-      <c r="I19" s="84" t="s">
+      <c r="I19" s="87" t="s">
         <v>338</v>
       </c>
-      <c r="J19" s="84"/>
-      <c r="K19" s="84"/>
+      <c r="J19" s="87"/>
+      <c r="K19" s="87"/>
       <c r="L19" s="32"/>
       <c r="M19" s="31"/>
     </row>
@@ -5195,17 +5195,17 @@
       <c r="B20" s="44" t="s">
         <v>334</v>
       </c>
-      <c r="C20" s="85" t="s">
+      <c r="C20" s="88" t="s">
         <v>340</v>
       </c>
-      <c r="D20" s="85"/>
+      <c r="D20" s="88"/>
       <c r="I20" s="34" t="s">
         <v>334</v>
       </c>
-      <c r="J20" s="85" t="s">
+      <c r="J20" s="88" t="s">
         <v>340</v>
       </c>
-      <c r="K20" s="85"/>
+      <c r="K20" s="88"/>
     </row>
     <row r="24" spans="1:13" s="41" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A24" s="43"/>
@@ -5319,10 +5319,10 @@
       <c r="B31" s="36"/>
       <c r="C31" s="36"/>
       <c r="D31" s="36"/>
-      <c r="E31" s="78"/>
-      <c r="F31" s="78"/>
-      <c r="G31" s="78"/>
-      <c r="H31" s="78"/>
+      <c r="E31" s="82"/>
+      <c r="F31" s="82"/>
+      <c r="G31" s="82"/>
+      <c r="H31" s="82"/>
       <c r="I31" s="42"/>
       <c r="J31" s="42"/>
       <c r="K31" s="36"/>
@@ -5334,10 +5334,10 @@
       <c r="B32" s="36"/>
       <c r="C32" s="36"/>
       <c r="D32" s="36"/>
-      <c r="E32" s="79"/>
-      <c r="F32" s="79"/>
-      <c r="G32" s="79"/>
-      <c r="H32" s="79"/>
+      <c r="E32" s="83"/>
+      <c r="F32" s="83"/>
+      <c r="G32" s="83"/>
+      <c r="H32" s="83"/>
       <c r="I32" s="42"/>
       <c r="J32" s="42"/>
       <c r="K32" s="36"/>
@@ -5349,12 +5349,12 @@
       <c r="B33" s="39"/>
       <c r="C33" s="38"/>
       <c r="D33" s="38"/>
-      <c r="E33" s="80" t="s">
+      <c r="E33" s="84" t="s">
         <v>336</v>
       </c>
-      <c r="F33" s="80"/>
-      <c r="G33" s="80"/>
-      <c r="H33" s="80"/>
+      <c r="F33" s="84"/>
+      <c r="G33" s="84"/>
+      <c r="H33" s="84"/>
       <c r="I33" s="37"/>
       <c r="J33" s="37"/>
       <c r="K33" s="36"/>
@@ -5364,12 +5364,6 @@
   </sheetData>
   <sheetProtection sheet="1"/>
   <mergeCells count="16">
-    <mergeCell ref="A11:M11"/>
-    <mergeCell ref="B2:M2"/>
-    <mergeCell ref="B3:M3"/>
-    <mergeCell ref="B4:M4"/>
-    <mergeCell ref="B5:M5"/>
-    <mergeCell ref="B10:M10"/>
     <mergeCell ref="E31:H31"/>
     <mergeCell ref="E32:H32"/>
     <mergeCell ref="E33:H33"/>
@@ -5380,6 +5374,12 @@
     <mergeCell ref="I19:K19"/>
     <mergeCell ref="C20:D20"/>
     <mergeCell ref="J20:K20"/>
+    <mergeCell ref="A11:M11"/>
+    <mergeCell ref="B2:M2"/>
+    <mergeCell ref="B3:M3"/>
+    <mergeCell ref="B4:M4"/>
+    <mergeCell ref="B5:M5"/>
+    <mergeCell ref="B10:M10"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="1" bottom="0.25" header="0.51180555555555551" footer="0.51180555555555551"/>
